--- a/Shared/XLS/Option.xlsx
+++ b/Shared/XLS/Option.xlsx
@@ -264,9 +264,6 @@
     <t>StatDetail_BlockRate_Add</t>
   </si>
   <si>
-    <t>StatDetail_MoveSpeedBonus_Add</t>
-  </si>
-  <si>
     <t>OPT_EXP_BONUS_ADD</t>
   </si>
   <si>
@@ -311,11 +308,15 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>OPT_MOVE_SPEED_BONUS_ADD</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
     <t>OPT_CRIT_RATE_ADD</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>OPT_MOVE_SPEED_ADD</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>StatDetail_MoveSpeed_Add</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -855,7 +856,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1069,7 +1070,7 @@
     </row>
     <row r="10" spans="1:5">
       <c r="B10" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C10" t="s">
         <v>3</v>
@@ -1080,7 +1081,7 @@
     </row>
     <row r="11" spans="1:5">
       <c r="B11" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C11" t="s">
         <v>3</v>
@@ -1136,13 +1137,13 @@
     </row>
     <row r="16" spans="1:5">
       <c r="B16" s="10" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C16" s="10" t="s">
         <v>3</v>
       </c>
       <c r="D16" s="10" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="17" spans="2:4">
@@ -1202,13 +1203,13 @@
     </row>
     <row r="22" spans="2:4">
       <c r="B22" s="10" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C22" s="10" t="s">
         <v>3</v>
       </c>
       <c r="D22" s="10" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="23" spans="2:4">
@@ -1307,51 +1308,51 @@
         <v>3</v>
       </c>
       <c r="D31" s="10" t="s">
-        <v>66</v>
+        <v>81</v>
       </c>
     </row>
     <row r="32" spans="2:4">
       <c r="B32" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="C32" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="D32" s="10" t="s">
         <v>67</v>
-      </c>
-      <c r="C32" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="D32" s="10" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="33" spans="2:5">
       <c r="B33" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="C33" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="D33" s="10" t="s">
         <v>69</v>
-      </c>
-      <c r="C33" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="D33" s="10" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="34" spans="2:5">
       <c r="B34" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="C34" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="D34" s="10" t="s">
         <v>71</v>
-      </c>
-      <c r="C34" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="D34" s="10" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="35" spans="2:5">
       <c r="B35" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="C35" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="D35" s="10" t="s">
         <v>73</v>
-      </c>
-      <c r="C35" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="D35" s="10" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="36" spans="2:5">

--- a/Shared/XLS/Option.xlsx
+++ b/Shared/XLS/Option.xlsx
@@ -292,31 +292,31 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
+    <t>StatDetail_Def_Add</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>OPT_DEF_ADD</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>OPT_ATK_SPEED_ADD</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>OPT_CRIT_RATE_ADD</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>OPT_MOVE_SPEED_ADD</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>StatDetail_MoveSpeed_Add</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
     <t>OPT_MAX_HP_ADD</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>StatDetail_Def_Add</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>OPT_DEF_ADD</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>OPT_ATK_SPEED_ADD</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>OPT_CRIT_RATE_ADD</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>OPT_MOVE_SPEED_ADD</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>StatDetail_MoveSpeed_Add</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -856,7 +856,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1070,7 +1070,7 @@
     </row>
     <row r="10" spans="1:5">
       <c r="B10" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C10" t="s">
         <v>3</v>
@@ -1081,7 +1081,7 @@
     </row>
     <row r="11" spans="1:5">
       <c r="B11" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C11" t="s">
         <v>3</v>
@@ -1137,7 +1137,7 @@
     </row>
     <row r="16" spans="1:5">
       <c r="B16" s="10" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="C16" s="10" t="s">
         <v>3</v>
@@ -1203,13 +1203,13 @@
     </row>
     <row r="22" spans="2:4">
       <c r="B22" s="10" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C22" s="10" t="s">
         <v>3</v>
       </c>
       <c r="D22" s="10" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="23" spans="2:4">
@@ -1302,13 +1302,13 @@
     </row>
     <row r="31" spans="2:4">
       <c r="B31" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="C31" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="D31" s="10" t="s">
         <v>80</v>
-      </c>
-      <c r="C31" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="D31" s="10" t="s">
-        <v>81</v>
       </c>
     </row>
     <row r="32" spans="2:4">
